--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260608.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,271,000</t>
+          <t>310,672</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>1,271,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,064,000</t>
+          <t>1,725,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,725,000</t>
+          <t>3,064,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,606,000</t>
+          <t>798,897</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>5,606,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>798,897</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>937,659</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>937,659</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,573,703</t>
+          <t>7,344,249</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,344,249</t>
+          <t>2,573,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202606WVHFM6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202606WVHFM6F</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>1,186,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,186,076</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,007,121</t>
+          <t>1,542,400</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,542,400</t>
+          <t>1,007,121</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>1,722,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,722,000</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
